--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,16 +462,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.02072307014706198</v>
+        <v>-0.04980140782663767</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2914414120732919</v>
+        <v>0.1731812252720874</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.1735604413007793</v>
+        <v>-0.3330318394752742</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.2487033280707368</v>
+        <v>-0.4596452212404349</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.222838640089139</v>
+        <v>0.1586656370683763</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.1052302493283743</v>
+        <v>-0.3535289108455092</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>47.14456205583915</v>
+        <v>23.64718637951443</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.3993803743721537</v>
+        <v>-0.2237109829066279</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.245787002197087</v>
+        <v>0.2898327784619215</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-2.095396275638525</v>
+        <v>-0.8162423494079177</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-2.649575872376186</v>
+        <v>-1.115476109074468</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4118231534635988</v>
+        <v>0.2764492945424496</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-1.000188049812801</v>
+        <v>-0.8384603393000234</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>55.14540890055351</v>
+        <v>38.34121805615116</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.135037317833913</v>
+        <v>-0.2360715992069162</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2156863957253621</v>
+        <v>0.2352288042967532</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.6616669474528402</v>
+        <v>-1.137257947523387</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.9124341054585812</v>
+        <v>-1.506122796929765</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2811190907631883</v>
+        <v>0.2838370325629629</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.4987455602899333</v>
+        <v>-0.8614977264228955</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>51.07246684630251</v>
+        <v>51.00439718491555</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.1462686165923134</v>
+        <v>0.003564929764462432</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2480036290628489</v>
+        <v>0.343760777402016</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.6020134776642287</v>
+        <v>0.1378684247719935</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.9416860770337203</v>
+        <v>0.2011733511784879</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2892314692291904</v>
+        <v>0.2177720835271006</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.5249403517486172</v>
+        <v>0.01704770403952503</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>67.35809001544264</v>
+        <v>53.90385761507171</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2889016470276542</v>
+        <v>0.259430273872604</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2644893804202901</v>
+        <v>0.2877031862558443</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.071890300710584</v>
+        <v>0.9248833577581393</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.505794068083417</v>
+        <v>1.284871847581218</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1997912828461615</v>
+        <v>0.2277086503084115</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.506942540555934</v>
+        <v>1.186760376537649</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>60.36430603680152</v>
+        <v>61.679689557343</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.5102093585728749</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.4075528208658917</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2.001864365099085</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>3.161558709975232</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1090106032623784</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>10.19600001280446</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>50.41898226241549</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>